--- a/AAII_Financials/Quarterly/RFAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFAC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>RFAC</t>
   </si>
@@ -1124,8 +1124,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>300</v>
       </c>
       <c r="E17" s="3">
         <v>600</v>
@@ -1544,8 +1544,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <v>-200</v>
@@ -1594,8 +1594,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <v>-200</v>
@@ -1894,8 +1894,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <v>-200</v>
@@ -1994,8 +1994,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <v>-200</v>
@@ -2689,8 +2689,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -3029,8 +3029,8 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>4000</v>
       </c>
       <c r="E60" s="3">
         <v>3600</v>
@@ -3800,7 +3800,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-3300</v>
+        <v>40100</v>
       </c>
       <c r="E76" s="3">
         <v>40100</v>
@@ -3954,8 +3954,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>0</v>
       </c>
       <c r="E81" s="3">
         <v>-200</v>

--- a/AAII_Financials/Quarterly/RFAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>RFAC</t>
   </si>
@@ -656,67 +656,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -732,8 +732,11 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -782,8 +785,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -832,8 +838,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -882,8 +891,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,8 +914,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -952,8 +965,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1002,8 +1018,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1052,8 +1071,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1102,8 +1124,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1119,22 +1144,23 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
         <v>300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>300</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
@@ -1143,7 +1169,7 @@
         <v>300</v>
       </c>
       <c r="J17" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -1151,8 +1177,8 @@
       <c r="L17" s="3">
         <v>0</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
@@ -1169,8 +1195,11 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1178,13 +1207,13 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-300</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
@@ -1193,7 +1222,7 @@
         <v>-300</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -1201,8 +1230,8 @@
       <c r="L18" s="3">
         <v>0</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
@@ -1219,8 +1248,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1239,8 +1271,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1251,28 +1284,28 @@
         <v>400</v>
       </c>
       <c r="F20" s="3">
+        <v>400</v>
+      </c>
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1289,8 +1322,11 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1298,14 +1334,14 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>400</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,8 +1375,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1389,40 +1428,43 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
         <v>0</v>
       </c>
       <c r="L23" s="3">
         <v>0</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>0</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
@@ -1439,8 +1481,11 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1451,17 +1496,17 @@
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1477,8 +1522,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1489,8 +1534,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1539,40 +1587,43 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
         <v>0</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
@@ -1589,40 +1640,43 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
       <c r="L27" s="3">
         <v>0</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>0</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
@@ -1639,8 +1693,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1689,8 +1746,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,8 +1799,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1789,8 +1852,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1839,8 +1905,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1851,28 +1920,28 @@
         <v>-400</v>
       </c>
       <c r="F32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1889,40 +1958,43 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
         <v>0</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
@@ -1939,8 +2011,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1989,40 +2064,43 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
         <v>0</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
@@ -2039,46 +2117,49 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2175,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2114,8 +2198,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2134,35 +2219,36 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2175,8 +2261,8 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q41" s="3">
         <v>0</v>
@@ -2184,8 +2270,11 @@
       <c r="R41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2234,8 +2323,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2284,8 +2376,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2334,8 +2429,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2343,10 +2441,10 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>300</v>
@@ -2361,14 +2459,14 @@
         <v>300</v>
       </c>
       <c r="K45" s="3">
+        <v>300</v>
+      </c>
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2384,41 +2482,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>200</v>
+      </c>
+      <c r="E46" s="3">
         <v>100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,35 +2535,38 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E47" s="3">
         <v>44000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>43200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>119100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>117700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>116800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>116300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>116200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,8 +2579,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2484,8 +2588,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2534,8 +2641,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2584,8 +2694,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2634,8 +2747,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2684,8 +2800,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2699,20 +2818,20 @@
         <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,8 +2844,8 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -2734,8 +2853,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2784,41 +2906,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E54" s="3">
         <v>44100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>119500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>118100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>117500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>118200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>300</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,8 +2959,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2854,8 +2982,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2874,40 +3003,41 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="E57" s="3">
         <v>900</v>
       </c>
       <c r="F57" s="3">
+        <v>900</v>
+      </c>
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2915,8 +3045,8 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -2924,23 +3054,26 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2953,8 +3086,8 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2974,41 +3107,44 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>77500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>500</v>
       </c>
       <c r="J59" s="3">
         <v>500</v>
       </c>
       <c r="K59" s="3">
+        <v>500</v>
+      </c>
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,41 +3160,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E60" s="3">
         <v>4000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>78400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,8 +3213,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3124,8 +3266,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3141,11 +3286,11 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -3162,8 +3307,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3174,8 +3319,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3224,8 +3372,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3274,8 +3425,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3324,41 +3478,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3374,8 +3531,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3394,8 +3554,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3444,8 +3605,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3494,8 +3658,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3544,8 +3711,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3594,22 +3764,25 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-200</v>
       </c>
       <c r="H72" s="3">
         <v>-200</v>
@@ -3618,16 +3791,16 @@
         <v>-200</v>
       </c>
       <c r="J72" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-100</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
       <c r="L72" s="3">
         <v>0</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
+      <c r="M72" s="3">
+        <v>0</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
@@ -3644,8 +3817,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3694,8 +3870,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3744,8 +3923,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3794,40 +3976,43 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>40100</v>
+        <v>24800</v>
       </c>
       <c r="E76" s="3">
         <v>40100</v>
       </c>
       <c r="F76" s="3">
+        <v>40100</v>
+      </c>
+      <c r="G76" s="3">
         <v>41100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>117000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>116600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>116500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>116600</v>
       </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
       <c r="L76" s="3">
         <v>0</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3">
+        <v>0</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
@@ -3844,8 +4029,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3894,46 +4082,49 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3949,40 +4140,43 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>0</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
@@ -3999,8 +4193,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4019,8 +4216,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4069,8 +4267,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4119,8 +4320,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4169,8 +4373,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4219,8 +4426,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4269,8 +4479,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4319,40 +4532,43 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>0</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
@@ -4360,8 +4576,8 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -4369,8 +4585,11 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4389,8 +4608,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4439,8 +4659,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4489,8 +4712,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4539,35 +4765,38 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>76300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-116200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4580,8 +4809,8 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -4589,8 +4818,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4609,8 +4841,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4659,8 +4892,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4709,8 +4945,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4759,8 +4998,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4809,23 +5051,26 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-75300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -4833,11 +5078,11 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>117700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4850,8 +5095,8 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -4859,8 +5104,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4909,40 +5157,43 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
-      </c>
-      <c r="E102" s="3">
-        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>100</v>
       </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
@@ -4950,13 +5201,16 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RFAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RFAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>RFAC</t>
   </si>
@@ -656,73 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -735,8 +737,14 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -788,8 +796,14 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -841,8 +855,14 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -894,8 +914,14 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -915,8 +941,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -968,8 +996,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1021,8 +1055,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1074,8 +1114,14 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1127,8 +1173,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1145,46 +1197,48 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>200</v>
+      </c>
+      <c r="F17" s="3">
         <v>900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L17" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
@@ -1198,8 +1252,14 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1207,37 +1267,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-300</v>
       </c>
       <c r="J18" s="3">
         <v>-300</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
@@ -1251,8 +1311,14 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1272,8 +1338,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1281,37 +1349,37 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>600</v>
+      </c>
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1325,8 +1393,14 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1337,17 +1411,17 @@
         <v>100</v>
       </c>
       <c r="F21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>100</v>
+      </c>
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>400</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,8 +1452,14 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1431,46 +1511,52 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <v>100</v>
       </c>
       <c r="F23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>100</v>
+      </c>
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
         <v>0</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
@@ -1484,8 +1570,14 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,20 +1591,20 @@
         <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1525,11 +1617,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1537,8 +1629,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1590,46 +1688,52 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-500</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
         <v>0</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
@@ -1643,46 +1747,52 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
         <v>0</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
@@ -1696,8 +1806,14 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1749,8 +1865,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1802,8 +1924,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1855,8 +1983,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1908,8 +2042,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1917,37 +2057,37 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1961,46 +2101,52 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
         <v>0</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
@@ -2014,8 +2160,14 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2067,46 +2219,52 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
         <v>0</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
@@ -2120,52 +2278,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2178,8 +2342,14 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2199,8 +2369,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2220,41 +2392,43 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
+        <v>200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1500</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2264,17 +2438,23 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2326,31 +2506,37 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2379,8 +2565,14 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2432,25 +2624,31 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
@@ -2462,16 +2660,16 @@
         <v>300</v>
       </c>
       <c r="L45" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="N45" s="3">
+        <v>600</v>
+      </c>
+      <c r="O45" s="3">
+        <v>300</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2485,8 +2683,14 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2494,38 +2698,38 @@
         <v>200</v>
       </c>
       <c r="E46" s="3">
+        <v>200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>200</v>
+      </c>
+      <c r="G46" s="3">
         <v>100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2538,41 +2742,47 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>30200</v>
+      </c>
+      <c r="F47" s="3">
         <v>29700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>44000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>43200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>119100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>117700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>116800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>116300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>116200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2582,17 +2792,23 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2644,8 +2860,14 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2697,8 +2919,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2750,8 +2978,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2803,16 +3037,22 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -2821,23 +3061,23 @@
         <v>0</v>
       </c>
       <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2847,17 +3087,23 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2909,47 +3155,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30400</v>
+      </c>
+      <c r="F54" s="3">
         <v>30000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>44100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>43700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>119500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>118100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>117500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>117200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>118200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>300</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,8 +3214,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2983,8 +3241,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3004,82 +3264,90 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,11 +3357,11 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3110,47 +3378,53 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>77500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3163,47 +3437,53 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F60" s="3">
         <v>5100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>78400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3496,14 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3269,8 +3555,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3289,14 +3581,14 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -3310,11 +3602,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -3322,8 +3614,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3375,8 +3673,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3428,8 +3732,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3481,47 +3791,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F66" s="3">
         <v>5100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>78400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3850,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3555,8 +3877,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3608,8 +3932,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3661,8 +3991,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3714,8 +4050,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3767,46 +4109,52 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-4700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-3300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-2700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-200</v>
       </c>
       <c r="J72" s="3">
         <v>-200</v>
       </c>
       <c r="K72" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L72" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M72" s="3">
         <v>-100</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
@@ -3820,8 +4168,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3873,8 +4227,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3926,8 +4286,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3979,8 +4345,14 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -3988,37 +4360,37 @@
         <v>24800</v>
       </c>
       <c r="E76" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F76" s="3">
+        <v>24800</v>
+      </c>
+      <c r="G76" s="3">
         <v>40100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>40100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>41100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>117000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>116600</v>
-      </c>
-      <c r="J76" s="3">
-        <v>116500</v>
       </c>
       <c r="K76" s="3">
         <v>116600</v>
       </c>
       <c r="L76" s="3">
-        <v>0</v>
+        <v>116500</v>
       </c>
       <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+        <v>116600</v>
+      </c>
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
+        <v>0</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
@@ -4032,8 +4404,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4085,52 +4463,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4143,46 +4527,52 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
         <v>0</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
+        <v>0</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
@@ -4196,8 +4586,14 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4217,8 +4613,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4270,8 +4668,14 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4323,8 +4727,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4376,8 +4786,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4429,8 +4845,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4482,8 +4904,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4535,61 +4963,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4609,8 +5049,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4662,8 +5104,14 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4715,8 +5163,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4768,41 +5222,47 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>14900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>76300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-116200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,17 +5272,23 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4842,8 +5308,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4895,8 +5363,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4948,8 +5422,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5001,8 +5481,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5054,41 +5540,47 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-13900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-75300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>117700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5098,17 +5590,23 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5160,57 +5658,69 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1500</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>
